--- a/Offres_Emploi_Genie_Industriel_Lean_2026.xlsx
+++ b/Offres_Emploi_Genie_Industriel_Lean_2026.xlsx
@@ -1616,28 +1616,28 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>INGENIEUR METHODES ET HES</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Hutchinson (groupe TotalEnergies)</t>
-        </is>
-      </c>
+          <t>Responsable méthodes</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Temps plein</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Non precise</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr"/>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>0 à 2 ans</t>
+        </is>
+      </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Industrie pétrolière et gazière</t>
+          <t>Facility management / Maintenance multitechnique</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>Méthodes / HSE</t>
+          <t>Méthodes</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>Il y a 20 jours</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/ingenieur-methodes-et-hes-at-totalenergies-4397716583</t>
+          <t>https://www.optioncarriere.ma/jobad/ma43f8aab1dfa1ba0d426db230038516b3</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>Activités Nous sommes 40 000 femmes et hommes à relever les défis de nos clients de l’automobile, l’aéronautique, la défense et l’industrie. Notre passion des défis et notre enthousiasme nous font imaginer, concevoir et produire des solutions performantes et innovantes en management des fluides, systèmes d’étanchéité et antivibratoires. Travailler chez Hutchinson, c’est être curieux de tout, contribuer à l’évolution des mobilités et à la diminution des émissions carbone. Rejoignez-nous et révélez ce qui vous anime ! Une entreprise française implantée à l’international (25 pays) : 170 ans d’his</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -1679,28 +1679,28 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Responsable méthodes</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr"/>
+          <t>INGENIEUR METHODES ET HES</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Hutchinson (groupe TotalEnergies)</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>0 à 2 ans</t>
-        </is>
-      </c>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Non precise</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1710,28 +1710,28 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Facility management / Maintenance multitechnique</t>
+          <t>Industrie pétrolière et gazière</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Méthodes</t>
+          <t>Méthodes / HSE</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Il y a 20 jours</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma43f8aab1dfa1ba0d426db230038516b3</t>
+          <t>https://ma.linkedin.com/jobs/view/ingenieur-methodes-et-hes-at-totalenergies-4397716583</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>Activités Nous sommes 40 000 femmes et hommes à relever les défis de nos clients de l’automobile, l’aéronautique, la défense et l’industrie. Notre passion des défis et notre enthousiasme nous font imaginer, concevoir et produire des solutions performantes et innovantes en management des fluides, systèmes d’étanchéité et antivibratoires. Travailler chez Hutchinson, c’est être curieux de tout, contribuer à l’évolution des mobilités et à la diminution des émissions carbone. Rejoignez-nous et révélez ce qui vous anime ! Une entreprise française implantée à l’international (25 pays) : 170 ans d’his</t>
         </is>
       </c>
     </row>
@@ -4737,17 +4737,17 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Responsable Excellence Opérationnelle et RSE</t>
+          <t>Responsable Production - Casablanca</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Royal Mansour Tamuda Bay</t>
+          <t>Ingelec</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
@@ -4755,10 +4755,14 @@
           <t>Experimente</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>2 à 5 ans</t>
+        </is>
+      </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Tetouan</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -4768,28 +4772,28 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Hôtellerie</t>
+          <t>Équipements électriques</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>Excellence opérationnelle / RSE</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>Hier 14:47</t>
         </is>
       </c>
       <c r="M4" s="11" t="inlineStr"/>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/responsable-excellence-op%C3%A9rationnelle-et-rse-at-royal-mansour-tamuda-bay-4448165498</t>
+          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10423832/Responsable-Production-Casablanca.html</t>
         </is>
       </c>
       <c r="O4" s="10" t="inlineStr">
         <is>
-          <t>Le Royal Mansour Tamuda Bay recrute un (e) Responsable Excellence Opérationnelle et RSE . Mission principale : Le/La Responsable Excellence Opérationnelle et RSE est la/le Garant(e) de l’Excellence Opérationnelle et du respect de la politique environnementale du groupe visant à respecter l’environnement, l’éthique et les problématiques sociétales au sein de l’hôtel et auprès de nos collaborateurs. Il/elle a la charge du suivi de la satisfaction clientèle et du respect des protocoles et des procédures de contrôle de la qualité des prestations proposées. Il/elle doit être force de propositions en apportant de nouvelles stratégies visant à protéger l’environnement, à réduire les émissions de gaz à effet de serre, améliorer la qualité de vie des salariés et proposer à notre clientèle des servi</t>
+          <t>Responsable Production - Casablanca Casablanca Publiée le: 1 Aug-22:41 Vue: 88 Annonce N°: 10423832 Nous recherchons un Responsable Production pour rejoindre notre équipe. Ce poste implique la gestion des opérations de production, dans un environnement industriel dynamique. Missions : Superviser les processus de production pour garantir leur efficacité et leur conformité aux normes. Optimiser les ressources humaines, matérielles et financières liées à la production. Collaborer avec les autres départements pour assurer une coordination efficace des activités. Profil recherché pour le poste : Responsable Production - Casablanca Ce poste Responsable Production nécessite un candidat expérimenté, capable de gérer efficacement les opérations de production tout en assurant une conformité rigoureu</t>
         </is>
       </c>
     </row>
@@ -4800,17 +4804,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Responsable Production - Casablanca</t>
+          <t>Responsable Excellence Opérationnelle et RSE</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Ingelec</t>
+          <t>Royal Mansour Tamuda Bay</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -4818,14 +4822,10 @@
           <t>Experimente</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2 à 5 ans</t>
-        </is>
-      </c>
+      <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tetouan</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -4835,28 +4835,28 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Équipements électriques</t>
+          <t>Hôtellerie</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Excellence opérationnelle / RSE</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Hier 14:47</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10423832/Responsable-Production-Casablanca.html</t>
+          <t>https://ma.linkedin.com/jobs/view/responsable-excellence-op%C3%A9rationnelle-et-rse-at-royal-mansour-tamuda-bay-4448165498</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Responsable Production - Casablanca Casablanca Publiée le: 1 Aug-22:41 Vue: 88 Annonce N°: 10423832 Nous recherchons un Responsable Production pour rejoindre notre équipe. Ce poste implique la gestion des opérations de production, dans un environnement industriel dynamique. Missions : Superviser les processus de production pour garantir leur efficacité et leur conformité aux normes. Optimiser les ressources humaines, matérielles et financières liées à la production. Collaborer avec les autres départements pour assurer une coordination efficace des activités. Profil recherché pour le poste : Responsable Production - Casablanca Ce poste Responsable Production nécessite un candidat expérimenté, capable de gérer efficacement les opérations de production tout en assurant une conformité rigoureu</t>
+          <t>Le Royal Mansour Tamuda Bay recrute un (e) Responsable Excellence Opérationnelle et RSE . Mission principale : Le/La Responsable Excellence Opérationnelle et RSE est la/le Garant(e) de l’Excellence Opérationnelle et du respect de la politique environnementale du groupe visant à respecter l’environnement, l’éthique et les problématiques sociétales au sein de l’hôtel et auprès de nos collaborateurs. Il/elle a la charge du suivi de la satisfaction clientèle et du respect des protocoles et des procédures de contrôle de la qualité des prestations proposées. Il/elle doit être force de propositions en apportant de nouvelles stratégies visant à protéger l’environnement, à réduire les émissions de gaz à effet de serre, améliorer la qualité de vie des salariés et proposer à notre clientèle des servi</t>
         </is>
       </c>
     </row>
@@ -5056,19 +5056,15 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Maintenance Soutien Logistique Intégré Confirmé (SLI) - H/F</t>
+          <t>Industrialization Leader | Kenitra (Morocco)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>LGM</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Temps plein</t>
-        </is>
-      </c>
+          <t>ALTEN Maroc</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -5076,12 +5072,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>3 à 5 ans</t>
+          <t>Expérience exigée (durée non précisée)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Kenitra</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -5091,28 +5087,28 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Conseil en ingénierie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Soutien logistique intégré / Maintenance</t>
+          <t>Industrialisation</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2 days ago</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-maintenance-soutien-logistique-int%C3%A9gr%C3%A9-confirm%C3%A9-sli-h-f-at-lgm-4438957821</t>
+          <t>https://www.bayt.com/en/morocco/jobs/industrialization-leader-kenitra-morocco-74956831/</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Maintenance Soutien Logistique Intégré Confirmé (SLI) - H/F LGM Casablanca, Casablanca-Settat, Maroc il y a 1 jour Postuler E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Enregistrer - La mission du Groupe LGM, c’est de concevoir pour les grands groupes industriels des solutions innovantes uniques (produits, organisationnelles ou technologiques), permettant d’améliorer les performances des grands systèmes et infrastructures complexes, durant les phases d’exploitation et de maintenance. LGM, c’est l’entité historique du Groupe, c’est par elle que tout a démarré, il y a 30 ans. Aujourd’hui, LGM ce sont près de 1100 collaborateurs présents en France et à l’international, qui analysent, optimisent et pilotent la conception,</t>
+          <t>Summary: Elevate your career as an Industrialization Flying Analyst at Alten Maroc, where a collaborative culture fosters innovation and efficiency. This role focuses on enhancing industrial processes for embedded electronic components, ensuring seamless integration between validation and production. Key responsibilities include managing project data, troubleshooting, and supporting engineering teams to resolve issues and improve processes.</t>
         </is>
       </c>
     </row>
@@ -5123,15 +5119,19 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Industrialization Leader | Kenitra (Morocco)</t>
+          <t>Ingénieur Maintenance Soutien Logistique Intégré Confirmé (SLI) - H/F</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>ALTEN Maroc</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr"/>
+          <t>LGM</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Expérience exigée (durée non précisée)</t>
+          <t>3 à 5 ans</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Kenitra</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -5154,28 +5154,28 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Conseil en ingénierie</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>Industrialisation</t>
+          <t>Soutien logistique intégré / Maintenance</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>2 days ago</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>https://www.bayt.com/en/morocco/jobs/industrialization-leader-kenitra-morocco-74956831/</t>
+          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-maintenance-soutien-logistique-int%C3%A9gr%C3%A9-confirm%C3%A9-sli-h-f-at-lgm-4438957821</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>Summary: Elevate your career as an Industrialization Flying Analyst at Alten Maroc, where a collaborative culture fosters innovation and efficiency. This role focuses on enhancing industrial processes for embedded electronic components, ensuring seamless integration between validation and production. Key responsibilities include managing project data, troubleshooting, and supporting engineering teams to resolve issues and improve processes.</t>
+          <t>Ingénieur Maintenance Soutien Logistique Intégré Confirmé (SLI) - H/F LGM Casablanca, Casablanca-Settat, Maroc il y a 1 jour Postuler E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Enregistrer - La mission du Groupe LGM, c’est de concevoir pour les grands groupes industriels des solutions innovantes uniques (produits, organisationnelles ou technologiques), permettant d’améliorer les performances des grands systèmes et infrastructures complexes, durant les phases d’exploitation et de maintenance. LGM, c’est l’entité historique du Groupe, c’est par elle que tout a démarré, il y a 30 ans. Aujourd’hui, LGM ce sont près de 1100 collaborateurs présents en France et à l’international, qui analysent, optimisent et pilotent la conception,</t>
         </is>
       </c>
     </row>
@@ -6861,19 +6861,15 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur(e) Bureau d'Etudes &amp; Industrialisation</t>
+          <t>Responsable Qualité et Affaires Réglementaire - Casablanca</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Temps plein</t>
-        </is>
-      </c>
+          <t>Profils Recrutement</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -6881,12 +6877,12 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>2 ans minimum</t>
+          <t>Minimum 3 ans</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -6896,28 +6892,28 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>Fabrication d'appareils électriques</t>
+          <t>Dispositifs médicaux</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>Bureau d'études / Industrialisation</t>
+          <t>Qualité / Affaires réglementaires</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>Il y a 9 jours</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-e-bureau-d-etudes-industrialisation-at-eaton-4425366701</t>
+          <t>https://www.optioncarriere.ma/jobad/ma30fbe17c933efcc1f7ef76feea39c43e</t>
         </is>
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
-          <t>Rejoindre Eaton Souriau Tanger, c’est intégrer un site industriel stratégique du groupe Eaton, spécialisé dans la conception et la fabrication de connecteurs de haute performance destinés aux secteurs aéronautique, industriel, automobile et médical. Notre site de Tanger regroupe plus de 750 collaborateurs et se distingue par son dynamisme, son environnement industriel moderne et son ouverture à l’innovation. A propos du poste Au sein des équipes Bureau d’Études / Industrialisation, vous intervenez sur la conception, le développement et l’industrialisation de produits destinés à des environneme</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -6928,15 +6924,19 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Responsable Qualité et Affaires Réglementaire - Casablanca</t>
+          <t>Ingénieur(e) Bureau d'Etudes &amp; Industrialisation</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Profils Recrutement</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr"/>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Minimum 3 ans</t>
+          <t>2 ans minimum</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -6959,28 +6959,28 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Dispositifs médicaux</t>
+          <t>Fabrication d'appareils électriques</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Qualité / Affaires réglementaires</t>
+          <t>Bureau d'études / Industrialisation</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Il y a 9 jours</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma30fbe17c933efcc1f7ef76feea39c43e</t>
+          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-e-bureau-d-etudes-industrialisation-at-eaton-4425366701</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>Rejoindre Eaton Souriau Tanger, c’est intégrer un site industriel stratégique du groupe Eaton, spécialisé dans la conception et la fabrication de connecteurs de haute performance destinés aux secteurs aéronautique, industriel, automobile et médical. Notre site de Tanger regroupe plus de 750 collaborateurs et se distingue par son dynamisme, son environnement industriel moderne et son ouverture à l’innovation. A propos du poste Au sein des équipes Bureau d’Études / Industrialisation, vous intervenez sur la conception, le développement et l’industrialisation de produits destinés à des environneme</t>
         </is>
       </c>
     </row>
@@ -8548,17 +8548,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur QHSE</t>
+          <t>Cutting/Crimping Equipment Engineer Meknes</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Aya Gold &amp; Silver</t>
+          <t>Lear Corporation</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>3 à 5 ans</t>
+          <t>3 ans</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Taliouine</t>
+          <t>Meknes</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -8583,32 +8583,28 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Mines</t>
+          <t>Câblage automobile</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>QHSE</t>
+          <t>Process / Équipements</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
+          <t>14 days ago</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-ingenieur-qhse-recrutement-aya-gold-silver-taliouine-184864.html</t>
+          <t>https://www.bayt.com/en/morocco/jobs/cutting-crimping-equipment-engineer-meknes-74877899/</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur QHSE - Taliouine Production / Qualité / Sécurité / Maintenance - Secteur Extraction / Mines Intermédiaire (3 à 5 ans) 1 poste(s) sur Agadir et région - Maroc Bac +5 et plus Minimum - Ecole d'ingénieur - Master Respect des règles Besoin d'objectivité Rationalisme Ténacité Organisation CDI Télétravail : Non Publiée il y a 7 jours sur ReKrute.com - Postulez avant le 21/09/2026 J'aime Suivre Entreprise : Aya Gold &amp; Silver est un producteur d’argent canadien en pleine croissance qui exerce ses activités au Royaume du Maroc. Aya est la seule société minière purement argentifère cotée à la Bourse de Toronto. Elle exploite la mine d’argent Zgounder à forte teneur et explore ses terrains situés le long de l’Accident Sud-Atlasique à fort potentiel, dont plusieurs renferment d’anciennes mines productrices et des ressources historiques. En plus de ses actifs miniers marocains, Aya détient</t>
+          <t>Summary: Elevate your career as a Cutting/Crimping Equipment Engineer in Meknes, Morocco, where innovation meets excellence. At Lear, we empower our teams to develop groundbreaking technologies and achieve remarkable success. Your expertise in cutting and crimping processes will play a crucial role in our mission to deliver high-quality products. Be part of a collaborative environment that values respect, inclusion, and continuous improvement.</t>
         </is>
       </c>
     </row>
@@ -8619,12 +8615,12 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Pilote configuration EE H/F</t>
+          <t>Ingénieur QHSE</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>ALTEN Maroc</t>
+          <t>Aya Gold &amp; Silver</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -8639,12 +8635,12 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>6 mois à 1 an</t>
+          <t>3 à 5 ans</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Tetouan</t>
+          <t>Taliouine</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -8654,12 +8650,12 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Mines</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>Gestion de configuration</t>
+          <t>QHSE</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
@@ -8674,12 +8670,12 @@
       </c>
       <c r="N62" s="12" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-pilote-configuration-ee-hf-recrutement-alten-maroc-tetouan-184873.html</t>
+          <t>https://www.rekrute.com/offre-emploi-ingenieur-qhse-recrutement-aya-gold-silver-taliouine-184864.html</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>Pilote configuration EE H/F - Tétouan Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles Débutant (-1 an) 2 poste(s) sur Tanger et région - Maroc Bac +5 et plus - Ecole d'ingénieur - Master Respect des règles Besoin d'objectivité Rationalisme Ténacité Organisation CDI Télétravail : Non Publiée il y a 7 jours sur ReKrute.com - Postulez avant le 21/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donneurs d’ordre internati</t>
+          <t>Ingénieur QHSE - Taliouine Production / Qualité / Sécurité / Maintenance - Secteur Extraction / Mines Intermédiaire (3 à 5 ans) 1 poste(s) sur Agadir et région - Maroc Bac +5 et plus Minimum - Ecole d'ingénieur - Master Respect des règles Besoin d'objectivité Rationalisme Ténacité Organisation CDI Télétravail : Non Publiée il y a 7 jours sur ReKrute.com - Postulez avant le 21/09/2026 J'aime Suivre Entreprise : Aya Gold &amp; Silver est un producteur d’argent canadien en pleine croissance qui exerce ses activités au Royaume du Maroc. Aya est la seule société minière purement argentifère cotée à la Bourse de Toronto. Elle exploite la mine d’argent Zgounder à forte teneur et explore ses terrains situés le long de l’Accident Sud-Atlasique à fort potentiel, dont plusieurs renferment d’anciennes mines productrices et des ressources historiques. En plus de ses actifs miniers marocains, Aya détient</t>
         </is>
       </c>
     </row>
@@ -8690,17 +8686,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Cutting/Crimping Equipment Engineer Meknes</t>
+          <t>Pilote configuration EE H/F</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Lear Corporation</t>
+          <t>ALTEN Maroc</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -8710,12 +8706,12 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>3 ans</t>
+          <t>6 mois à 1 an</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Meknes</t>
+          <t>Tetouan</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -8725,28 +8721,32 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Câblage automobile</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Process / Équipements</t>
+          <t>Gestion de configuration</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>14 days ago</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr"/>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>https://www.bayt.com/en/morocco/jobs/cutting-crimping-equipment-engineer-meknes-74877899/</t>
+          <t>https://www.rekrute.com/offre-emploi-pilote-configuration-ee-hf-recrutement-alten-maroc-tetouan-184873.html</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>Summary: Elevate your career as a Cutting/Crimping Equipment Engineer in Meknes, Morocco, where innovation meets excellence. At Lear, we empower our teams to develop groundbreaking technologies and achieve remarkable success. Your expertise in cutting and crimping processes will play a crucial role in our mission to deliver high-quality products. Be part of a collaborative environment that values respect, inclusion, and continuous improvement.</t>
+          <t>Pilote configuration EE H/F - Tétouan Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles Débutant (-1 an) 2 poste(s) sur Tanger et région - Maroc Bac +5 et plus - Ecole d'ingénieur - Master Respect des règles Besoin d'objectivité Rationalisme Ténacité Organisation CDI Télétravail : Non Publiée il y a 7 jours sur ReKrute.com - Postulez avant le 21/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donneurs d’ordre internati</t>
         </is>
       </c>
     </row>
@@ -9025,17 +9025,17 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Méthodes &amp; Industrialisation</t>
+          <t>Ingénieur Qualité | Fés</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>Best Profil</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Intérim</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>3 à 8 ans</t>
+          <t>Expérience obligatoire (durée non précisée)</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Rabat</t>
+          <t>Fes</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -9060,28 +9060,28 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Aéronautique / Spatial / Automobile</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>Méthodes / Industrialisation</t>
+          <t>Qualité</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>Il y a 15 jours</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr"/>
       <c r="N68" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-m%C3%A9thodes-industrialisation-at-alten-4440131128</t>
+          <t>https://www.optioncarriere.ma/jobad/mafa428536bce3dbc11f60bd40ffa4e78c</t>
         </is>
       </c>
       <c r="O68" s="10" t="inlineStr">
         <is>
-          <t>ALTEN DELIVERY CENTER MAROC, Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2300 consultants et vise un centre d’excellence de 3300 consultants ALTENiens en fin 2027. ALTEN Maroc est désormais un acteur majeur de l’insertion professionnelle des ingénieurs. Nous accompagnons nos clients, leaders de l’Industrie dans leurs stratégies de développement dans les domaines de l’automobile, du ferroviaire, de l’IT, de la R&amp;D et des Télécoms &amp; Médias. Rejoindre ALTEN MAROC c’est bénéficier : D</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Méthodes &amp; Industrialisation</t>
+          <t>Responsable Supply Chain H/F | Casablanca</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>ALTEN Maroc</t>
+          <t>Best Profil</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -9112,12 +9112,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>3 à 8 ans</t>
+          <t>8 à 12 ans</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Rabat</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -9127,32 +9127,28 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Aéronautique / Spatial / Automobile</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Méthodes / Industrialisation</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
+          <t>Il y a 15 jours</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-ingenieur-methodes-industrialisation-recrutement-alten-maroc-rabat-184807.html</t>
+          <t>https://www.optioncarriere.ma/jobad/maf0d002ad8f25512fa4f60188a3c767c0</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Méthodes &amp; Industrialisation - Rabat Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles - Automobile / Motos / Cycles Confirmé (5 à 10 ans) 1 poste(s) sur Rabat et région - Maroc Bac +5 et plus Minimum Besoin d'objectivité Ténacité Organisation Rationalisme Respect des règles CDI Télétravail : Non Publiée il y a 8 jours sur ReKrute.com - Postulez avant le 20/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donn</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -9163,17 +9159,17 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Customer Quality Engineer</t>
+          <t>Ingénieur Méthodes &amp; Industrialisation</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Hirschmann Automotive</t>
+          <t>ALTEN</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -9183,12 +9179,12 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>6 mois minimum (ou stage)</t>
+          <t>3 à 8 ans</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Oujda</t>
+          <t>Rabat</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -9198,12 +9194,12 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Aéronautique / Spatial / Automobile</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>Qualité client</t>
+          <t>Méthodes / Industrialisation</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
@@ -9214,12 +9210,12 @@
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/customer-quality-engineer-at-hirschmann-automotive-4440142746</t>
+          <t>https://ma.linkedin.com/jobs/view/ing%C3%A9nieur-m%C3%A9thodes-industrialisation-at-alten-4440131128</t>
         </is>
       </c>
       <c r="O70" s="10" t="inlineStr">
         <is>
-          <t># Skillcheck : BAC +5/ Engineer Diploma. At least 6 months experience/Internship in the Automotive industry. Customer oriented abilities &amp; Data analysis spirt. Strong autonomy, excellent time management, and effective leadership skills. A good knowledge of quality norms &amp; standards (IATF16949, VDA, Quality core tools, CSR,…). Knowledge of SAP &amp; Customer portals. Good knowledge of Quality tools (Problem solving methodology, 8D, 5Why’s…). Good communication and negotiation skills. Perfect command of spoken and written English. # Challengecheck: Responsible for the complaints and escalations hand</t>
+          <t>ALTEN DELIVERY CENTER MAROC, Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2300 consultants et vise un centre d’excellence de 3300 consultants ALTENiens en fin 2027. ALTEN Maroc est désormais un acteur majeur de l’insertion professionnelle des ingénieurs. Nous accompagnons nos clients, leaders de l’Industrie dans leurs stratégies de développement dans les domaines de l’automobile, du ferroviaire, de l’IT, de la R&amp;D et des Télécoms &amp; Médias. Rejoindre ALTEN MAROC c’est bénéficier : D</t>
         </is>
       </c>
     </row>
@@ -9230,17 +9226,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Supply Chain PTM (Wipers Activity) M/F</t>
+          <t>Ingénieur Méthodes &amp; Industrialisation</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Valeo</t>
+          <t>ALTEN Maroc</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr">
@@ -9250,12 +9246,12 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Minimum 2 ans</t>
+          <t>3 à 8 ans</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Rabat</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -9265,28 +9261,32 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Équipementier automobile</t>
+          <t>Aéronautique / Spatial / Automobile</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Méthodes / Industrialisation</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="inlineStr"/>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/supply-chain-ptm-wipers-activity-m-f-at-valeo-4440137290</t>
+          <t>https://www.rekrute.com/offre-emploi-ingenieur-methodes-industrialisation-recrutement-alten-maroc-rabat-184807.html</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>Who We Are ✌️ Valeo is a global technology company developing solutions that shape the future of mobility. We work with major automotive and mobility players to deliver cleaner, safer, and smarter technologies. We innovate constantly, but always with a practical mindset — our ideas need to survive the reality of the shopfloor, not just look impressive in presentations. Why Join Us 🤗 Joining Valeo means becoming part of a team where you can grow, learn, and contribute to projects that have real industrial impact. You’ll face meaningful challenges, collaborate with supportive colleagues, and dev</t>
+          <t>Ingénieur Méthodes &amp; Industrialisation - Rabat Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles - Automobile / Motos / Cycles Confirmé (5 à 10 ans) 1 poste(s) sur Rabat et région - Maroc Bac +5 et plus Minimum Besoin d'objectivité Ténacité Organisation Rationalisme Respect des règles CDI Télétravail : Non Publiée il y a 8 jours sur ReKrute.com - Postulez avant le 20/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donn</t>
         </is>
       </c>
     </row>
@@ -9297,17 +9297,17 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Qualité | Fés</t>
+          <t>Customer Quality Engineer</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Best Profil</t>
+          <t>Hirschmann Automotive</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Intérim</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Expérience obligatoire (durée non précisée)</t>
+          <t>6 mois minimum (ou stage)</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Fes</t>
+          <t>Oujda</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -9332,28 +9332,28 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>Qualité</t>
+          <t>Qualité client</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>Il y a 15 jours</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mafa428536bce3dbc11f60bd40ffa4e78c</t>
+          <t>https://ma.linkedin.com/jobs/view/customer-quality-engineer-at-hirschmann-automotive-4440142746</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t># Skillcheck : BAC +5/ Engineer Diploma. At least 6 months experience/Internship in the Automotive industry. Customer oriented abilities &amp; Data analysis spirt. Strong autonomy, excellent time management, and effective leadership skills. A good knowledge of quality norms &amp; standards (IATF16949, VDA, Quality core tools, CSR,…). Knowledge of SAP &amp; Customer portals. Good knowledge of Quality tools (Problem solving methodology, 8D, 5Why’s…). Good communication and negotiation skills. Perfect command of spoken and written English. # Challengecheck: Responsible for the complaints and escalations hand</t>
         </is>
       </c>
     </row>
@@ -9364,17 +9364,17 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Responsable Supply Chain H/F | Casablanca</t>
+          <t>Supply Chain PTM (Wipers Activity) M/F</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Best Profil</t>
+          <t>Valeo</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>8 à 12 ans</t>
+          <t>Minimum 2 ans</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Équipementier automobile</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -9409,18 +9409,18 @@
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>Il y a 15 jours</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/maf0d002ad8f25512fa4f60188a3c767c0</t>
+          <t>https://ma.linkedin.com/jobs/view/supply-chain-ptm-wipers-activity-m-f-at-valeo-4440137290</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>Who We Are ✌️ Valeo is a global technology company developing solutions that shape the future of mobility. We work with major automotive and mobility players to deliver cleaner, safer, and smarter technologies. We innovate constantly, but always with a practical mindset — our ideas need to survive the reality of the shopfloor, not just look impressive in presentations. Why Join Us 🤗 Joining Valeo means becoming part of a team where you can grow, learn, and contribute to projects that have real industrial impact. You’ll face meaningful challenges, collaborate with supportive colleagues, and dev</t>
         </is>
       </c>
     </row>
@@ -9549,19 +9549,11 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Tactical planning Consultant</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>ALTEN Maroc</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Responsable Supply Chain | Casablanca (Maroc)</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr"/>
+      <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -9569,12 +9561,12 @@
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>1 à 3 ans</t>
+          <t>Expérience en supply chain industrielle (durée non précisée)</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Tetouan</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -9584,32 +9576,28 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Agroalimentaire (biscuiterie / chocolaterie)</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>Planification tactique</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="M76" s="11" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
+          <t>Il y a 18 jours</t>
+        </is>
+      </c>
+      <c r="M76" s="11" t="inlineStr"/>
       <c r="N76" s="12" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-tactical-planning-consultant-recrutement-alten-maroc-tetouan-184646.html</t>
+          <t>https://www.optioncarriere.ma/jobad/ma5f20f3a99d39e8086486458761fb7f9f</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
         <is>
-          <t>Tactical planning Consultant - Tetouan Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles - Automobile / Motos / Cycles Confirmé (5 à 10 ans) 1 poste(s) sur Autres régions - Maroc Bac +5 et plus Minimum Besoin d'objectivité Ténacité Organisation Rationalisme Respect des règles CDI Télétravail : Non Publiée il y a 11 jours sur ReKrute.com - Postulez avant le 17/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donneurs d’o</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9608,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur automatisation</t>
+          <t>Tactical planning Consultant</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -9640,12 +9628,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>3 à 4 ans</t>
+          <t>1 à 3 ans</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Kenitra</t>
+          <t>Tetouan</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -9660,7 +9648,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Automatisation</t>
+          <t>Planification tactique</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -9675,12 +9663,12 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>https://ma.jooble.org/desc/4982385296795592466?ckey=lean&amp;rgn=-1&amp;pos=2&amp;elckey=-5385399171710788904&amp;pageType=20&amp;p=1&amp;sid=4520762529071493932&amp;jobAge=380&amp;relb=100&amp;brelb=100&amp;bscr=528.1947&amp;scr=528.1947&amp;iid=-1250874496165211365</t>
+          <t>https://www.rekrute.com/offre-emploi-tactical-planning-consultant-recrutement-alten-maroc-tetouan-184646.html</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur automatisation ... lectriques . Connaissances en robotique . Connaissances des technologies de commande des convoyeurs . Connaissance des outils Lean Manufacturing et des outils de résolution de problèmes . Maîtrise des outils bureautiques , notamment Microsoft Excel et ... Signaler ALTEN Kenitra 15 days ago</t>
+          <t>Tactical planning Consultant - Tetouan Production / Qualité / Sécurité / Maintenance - Secteur Automobile / Motos / Cycles - Automobile / Motos / Cycles Confirmé (5 à 10 ans) 1 poste(s) sur Autres régions - Maroc Bac +5 et plus Minimum Besoin d'objectivité Ténacité Organisation Rationalisme Respect des règles CDI Télétravail : Non Publiée il y a 11 jours sur ReKrute.com - Postulez avant le 17/09/2026 J'aime Suivre Entreprise : ALTEN MAROC , Filiale du leader mondial de l’ingénierie et du conseil en technologie créé en 2008 et présent à Fès, Rabat, Tétouan et Casablanca, compte aujourd’hui plus de 2200 collaborateurs et vise un centre d’excellence de 3300 ALTENiens en fin 2027 . Elle s’impose aujourd’hui comme un acteur stratégique dans l’accompagnement du développement professionnel des ingénieurs. Notre mission : répondre aux ambitions technologiques de nos clients — grands donneurs d’o</t>
         </is>
       </c>
     </row>
@@ -9691,17 +9679,17 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Ingénieur automatisation</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Harmattan AI</t>
+          <t>ALTEN Maroc</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -9709,10 +9697,14 @@
           <t>Experimente</t>
         </is>
       </c>
-      <c r="G78" s="11" t="inlineStr"/>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>3 à 4 ans</t>
+        </is>
+      </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Maroc</t>
+          <t>Kenitra</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -9722,28 +9714,32 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>Aéronautique / Défense</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Automatisation</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="M78" s="11" t="inlineStr"/>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="N78" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/operations-manager-at-harmattan-ai-4441960541</t>
+          <t>https://ma.jooble.org/desc/4982385296795592466?ckey=lean&amp;rgn=-1&amp;pos=2&amp;elckey=-5385399171710788904&amp;pageType=20&amp;p=1&amp;sid=4520762529071493932&amp;jobAge=380&amp;relb=100&amp;brelb=100&amp;bscr=528.1947&amp;scr=528.1947&amp;iid=-1250874496165211365</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
         <is>
-          <t>About Us Harmattan AI is a next-generation defense prime building autonomous and scalable defense systems. Following the close of a $200M Series B, valuing the company at $1.4 billion, we are expanding our teams and capabilities to deliver mission-critical systems to allied forces. Our work is guided by clear values: building technologies with real-world impact, pursuing excellence in everything we do, setting ambitious goals, and taking on the hardest technical challenges. We operate in a demanding environment where rigor, ownership, and execution are expected. About The Role As an Operations</t>
+          <t>Ingénieur automatisation ... lectriques . Connaissances en robotique . Connaissances des technologies de commande des convoyeurs . Connaissance des outils Lean Manufacturing et des outils de résolution de problèmes . Maîtrise des outils bureautiques , notamment Microsoft Excel et ... Signaler ALTEN Kenitra 15 days ago</t>
         </is>
       </c>
     </row>
@@ -9754,24 +9750,28 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Responsable Supply Chain | Casablanca (Maroc)</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr"/>
-      <c r="E79" s="6" t="inlineStr"/>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Harmattan AI</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Expérience en supply chain industrielle (durée non précisée)</t>
-        </is>
-      </c>
+      <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Maroc</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -9781,28 +9781,28 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Agroalimentaire (biscuiterie / chocolaterie)</t>
+          <t>Aéronautique / Défense</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>Il y a 18 jours</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma5f20f3a99d39e8086486458761fb7f9f</t>
+          <t>https://ma.linkedin.com/jobs/view/operations-manager-at-harmattan-ai-4441960541</t>
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>About Us Harmattan AI is a next-generation defense prime building autonomous and scalable defense systems. Following the close of a $200M Series B, valuing the company at $1.4 billion, we are expanding our teams and capabilities to deliver mission-critical systems to allied forces. Our work is guided by clear values: building technologies with real-world impact, pursuing excellence in everything we do, setting ambitious goals, and taking on the hardest technical challenges. We operate in a demanding environment where rigor, ownership, and execution are expected. About The Role As an Operations</t>
         </is>
       </c>
     </row>
@@ -9813,19 +9813,15 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Chargé(e) de Qualité</t>
+          <t>Manager Supply Chain - Mohammedia</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Confidentiel (annonce anonyme)</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Briqueterie Jbel Annour</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -9833,7 +9829,7 @@
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>5 à 10 ans</t>
+          <t>5 à 10 ans ou plus</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -9848,32 +9844,28 @@
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>Électricité / Comptage d'eau</t>
+          <t>BTP / Matériaux de construction</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>Qualité / SMI</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
-      <c r="M80" s="11" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
+          <t>Il y a 19 jours</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="inlineStr"/>
       <c r="N80" s="12" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-chargee-de-qualite-recrutement-confidentiel-mohammedia-184602.html</t>
+          <t>https://www.optioncarriere.ma/jobad/ma1466e7a515b5deb040bad2c9cea5df39</t>
         </is>
       </c>
       <c r="O80" s="10" t="inlineStr">
         <is>
-          <t>Chargé(e) de Qualité - Mohammédia Production / Qualité / Sécurité / Maintenance - Secteur Electricité - Autres Industries Confirmé (5 à 10 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +5 et plus Minimum - Ecole d'ingénieur - Université Respect des règles Besoin d'objectivité Rationalisme Ténacité Besoin de réflexion Travail en équipe Implication au travail Organisation CDI Télétravail : Non Publiée il y a 12 jours sur ReKrute.com - Postulez avant le 16/09/2026 J'aime Entreprise : Entreprise industrielle Marocaine, implantés à Mohammedia, nous faisons partie de l’un des plus grands groupes privés du Royaume, actif dans plusieurs secteurs stratégiques. Spécialisés dans la fabrication de solutions de comptage d’eau et d’équipements pour les réseaux d’eau potable, nous bénéficions de plus de 78 ans d’expérience au service de l'environnement. Poste : En tant que Chargé(e) de Qualité,</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -9884,17 +9876,17 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Chargé(e) de Qualité</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Confidentiel (annonce anonyme)</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr">
@@ -9904,12 +9896,12 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2 ans</t>
+          <t>5 à 10 ans</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Maroc</t>
+          <t>Mohammedia</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -9919,28 +9911,32 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Électricité / Comptage d'eau</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Process / Industrialisation</t>
+          <t>Qualité / SMI</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr"/>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/process-engineer-at-aptiv-4440829736</t>
+          <t>https://www.rekrute.com/offre-emploi-chargee-de-qualite-recrutement-confidentiel-mohammedia-184602.html</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>Why join Aptiv? You'll have the opportunity to work on cutting-edge applications, develop breakthrough technologies, and deliver innovative solutions to some of the world’s leading automotive brands. See your work come to life on the road—helping make mobility safer, greener, and more connected. Ready to shape the future of mobility with us? We are currently looking for a Process Engineer Process Development &amp; optimization : Design, validate and implement automated testing system and vision inspection systems for manufacturing Lines. Develop testing methods for mechanical, electrical, or funct</t>
+          <t>Chargé(e) de Qualité - Mohammédia Production / Qualité / Sécurité / Maintenance - Secteur Electricité - Autres Industries Confirmé (5 à 10 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +5 et plus Minimum - Ecole d'ingénieur - Université Respect des règles Besoin d'objectivité Rationalisme Ténacité Besoin de réflexion Travail en équipe Implication au travail Organisation CDI Télétravail : Non Publiée il y a 12 jours sur ReKrute.com - Postulez avant le 16/09/2026 J'aime Entreprise : Entreprise industrielle Marocaine, implantés à Mohammedia, nous faisons partie de l’un des plus grands groupes privés du Royaume, actif dans plusieurs secteurs stratégiques. Spécialisés dans la fabrication de solutions de comptage d’eau et d’équipements pour les réseaux d’eau potable, nous bénéficions de plus de 78 ans d’expérience au service de l'environnement. Poste : En tant que Chargé(e) de Qualité,</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9947,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -9971,7 +9967,7 @@
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>5 à 10 ans</t>
+          <t>2 ans</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -9991,7 +9987,7 @@
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Process / Industrialisation</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
@@ -10002,12 +9998,12 @@
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/operations-manager-at-aptiv-4434072749</t>
+          <t>https://ma.linkedin.com/jobs/view/process-engineer-at-aptiv-4440829736</t>
         </is>
       </c>
       <c r="O82" s="10" t="inlineStr">
         <is>
-          <t>We are currently looking for an Operations Manager to manage and coordinate all activities in respective Plant Operational areas including development and implementation of manufacturing processes to maintain proper product functionality and cost efficiency. Work as key team member of the plant to achieve plant targets. This has to be based on agreed KPI in line with regional standards and policies. Main duties and expected results in this function Manages – leads and develops – of direct reports (Business Line management members) and be part of plant management team with responsibility of ove</t>
+          <t>Why join Aptiv? You'll have the opportunity to work on cutting-edge applications, develop breakthrough technologies, and deliver innovative solutions to some of the world’s leading automotive brands. See your work come to life on the road—helping make mobility safer, greener, and more connected. Ready to shape the future of mobility with us? We are currently looking for a Process Engineer Process Development &amp; optimization : Design, validate and implement automated testing system and vision inspection systems for manufacturing Lines. Develop testing methods for mechanical, electrical, or funct</t>
         </is>
       </c>
     </row>
@@ -10018,15 +10014,19 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Manager Supply Chain - Mohammedia</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Briqueterie Jbel Annour</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr"/>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
       <c r="F83" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>5 à 10 ans ou plus</t>
+          <t>5 à 10 ans</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Mohammedia</t>
+          <t>Maroc</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -10049,28 +10049,28 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>BTP / Matériaux de construction</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>Il y a 19 jours</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma1466e7a515b5deb040bad2c9cea5df39</t>
+          <t>https://ma.linkedin.com/jobs/view/operations-manager-at-aptiv-4434072749</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>We are currently looking for an Operations Manager to manage and coordinate all activities in respective Plant Operational areas including development and implementation of manufacturing processes to maintain proper product functionality and cost efficiency. Work as key team member of the plant to achieve plant targets. This has to be based on agreed KPI in line with regional standards and policies. Main duties and expected results in this function Manages – leads and develops – of direct reports (Business Line management members) and be part of plant management team with responsibility of ove</t>
         </is>
       </c>
     </row>
@@ -11082,19 +11082,15 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Continuous Improvement Specialist</t>
+          <t>Ingénieur qualité process</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>Temps plein</t>
-        </is>
-      </c>
+          <t>Talents Partners</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr"/>
       <c r="F99" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -11102,12 +11098,12 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>3 à 5 ans</t>
+          <t>Minimum 5 ans</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -11117,28 +11113,28 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Fabrication d'appareils électriques</t>
+          <t>Automobile (caoutchouc)</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>Amélioration continue</t>
+          <t>Qualité process</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>Il y a 27 jours</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/continuous-improvement-specialist-at-eaton-4426824937</t>
+          <t>https://www.optioncarriere.ma/jobad/ma8a7ab40f2b7f3e8b96a4bdf42ad1499f</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
         <is>
-          <t>At Eaton, we’re committed to improving the quality of life and the environment through intelligent power management technologies. With operations in over 175 countries, we help customers manage electrical, hydraulic, and mechanical power more efficiently, safely, and sustainably. Our culture is built on innovation, inclusion, and a shared purpose to make what matters work. As a CI Specialist , you will act as a key driver of Continuous Improvement across the plant, leading the development and deployment of a robust CI strategy, with a strong focus on ELSS initiatives and overall coordination o</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -11149,17 +11145,17 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Responsable de Site</t>
+          <t>Continuous Improvement Specialist</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Meski Invest - Riva Industries</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -11169,12 +11165,12 @@
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>5 à 10 ans</t>
+          <t>3 à 5 ans</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>El Jadida</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -11184,32 +11180,28 @@
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>Sidérurgie / Automobile</t>
+          <t>Fabrication d'appareils électriques</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Direction de site</t>
+          <t>Amélioration continue</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="M100" s="11" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="12" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-responsable-de-site-recrutement-meski-invest---riva-industries-el-jadida-184321.html</t>
+          <t>https://ma.linkedin.com/jobs/view/continuous-improvement-specialist-at-eaton-4426824937</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
         <is>
-          <t>Responsable de Site - El Jadida Banque (métiers de la) - Secteur Automobile / Motos / Cycles - Banque / Finance Confirmé (5 à 10 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +5 et plus Minimum Volonté de persuasion Conventionnel Flexibilité Implication au travail CDI Télétravail : Non Poste avec Management Publiée il y a 20 jours sur ReKrute.com - Postulez avant le 08/09/2026 J'aime Suivre Entreprise : Fort d’une expérience terrain de plus de 40 ans , MESKI Invest est un groupe marocain multi-métiers ayant fait le choix stratégique de la diversification , en intervenant dans les secteurs clés de l’économie marocaine : • Riva Industrie : Industries sidérurgiques • Entreprises Belmekki : Distribution de matériaux de construction • Nadym : Logistique et services de transport routier, transport de marchandises et location camions remorques • Belmekkimmo : Immobilier • Danub : Locatio</t>
+          <t>At Eaton, we’re committed to improving the quality of life and the environment through intelligent power management technologies. With operations in over 175 countries, we help customers manage electrical, hydraulic, and mechanical power more efficiently, safely, and sustainably. Our culture is built on innovation, inclusion, and a shared purpose to make what matters work. As a CI Specialist , you will act as a key driver of Continuous Improvement across the plant, leading the development and deployment of a robust CI strategy, with a strong focus on ELSS initiatives and overall coordination o</t>
         </is>
       </c>
     </row>
@@ -11220,12 +11212,12 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Responsable Supply Chain</t>
+          <t>Responsable de Site</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Confidentiel (annonce anonyme)</t>
+          <t>Meski Invest - Riva Industries</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -11240,12 +11232,12 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Junior (1 à 3 ans)</t>
+          <t>5 à 10 ans</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>El Jadida</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -11255,12 +11247,12 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Agroalimentaire</t>
+          <t>Sidérurgie / Automobile</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>Achats / Supply Chain</t>
+          <t>Direction de site</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -11275,12 +11267,12 @@
       </c>
       <c r="N101" s="8" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-responsable-supply-chain-recrutement-confidentiel-casablanca-184331.html</t>
+          <t>https://www.rekrute.com/offre-emploi-responsable-de-site-recrutement-meski-invest---riva-industries-el-jadida-184321.html</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
-          <t>Responsable Supply Chain - Casablanca Achats / Supply Chain - Secteur Agroalimentaire Junior (1 à 3 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +2 Minimum - Ecole de commerce Recherche de nouveauté Respect des règles Besoin d'objectivité Distance émotionnelle Rationalisme Ténacité Besoin d'action Organisation CDI Télétravail : Non Poste avec Management Publiée il y a 20 jours sur ReKrute.com - Postulez avant le 08/09/2026 J'aime Entreprise : Notre société est une entreprise industrielle spécialisée dans la fabrication de biscuits et chocolat. Elle dispose d’un outil de production moderne et en développement constant, conçu pour répondre aux exigences de qualité, de régularité et de performance industrielle. Poste : * Planification et ordonnancement de la production * Gestion des approvisionnements et des stocks * Optimisation des flux logistiques et livraisons clients * Améliora</t>
+          <t>Responsable de Site - El Jadida Banque (métiers de la) - Secteur Automobile / Motos / Cycles - Banque / Finance Confirmé (5 à 10 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +5 et plus Minimum Volonté de persuasion Conventionnel Flexibilité Implication au travail CDI Télétravail : Non Poste avec Management Publiée il y a 20 jours sur ReKrute.com - Postulez avant le 08/09/2026 J'aime Suivre Entreprise : Fort d’une expérience terrain de plus de 40 ans , MESKI Invest est un groupe marocain multi-métiers ayant fait le choix stratégique de la diversification , en intervenant dans les secteurs clés de l’économie marocaine : • Riva Industrie : Industries sidérurgiques • Entreprises Belmekki : Distribution de matériaux de construction • Nadym : Logistique et services de transport routier, transport de marchandises et location camions remorques • Belmekkimmo : Immobilier • Danub : Locatio</t>
         </is>
       </c>
     </row>
@@ -11291,12 +11283,12 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Responsable Production Senior (H/F) Secteur Aéronautique</t>
+          <t>Responsable Supply Chain</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Y STRATEGIE</t>
+          <t>Confidentiel (annonce anonyme)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -11311,12 +11303,12 @@
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>Profil senior</t>
+          <t>Junior (1 à 3 ans)</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Bouskoura</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -11326,28 +11318,32 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>Aéronautique</t>
+          <t>Agroalimentaire</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Achats / Supply Chain</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="M102" s="11" t="inlineStr"/>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
       <c r="N102" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/responsable-production-senior-h-f-secteur-a%C3%A9ronautique-at-y-strategie-4436891067</t>
+          <t>https://www.rekrute.com/offre-emploi-responsable-supply-chain-recrutement-confidentiel-casablanca-184331.html</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
         <is>
-          <t>Responsable Production Senior (H/F) Casablanca – Bouskoura Notre client est un groupe industriel international de premier plan, spécialisé dans la conception et la fabrication de solutions électroniques et de systèmes d'interconnexion destinés aux secteurs de l'aérospatial, de l'aéronautique, de la défense et des environnements critiques. Dans le cadre du développement de son site de production basé à Casablanca – Bouskoura, il recrute un(e) Responsable Production Senior . Votre mission Rattaché(e) à la Direction Générale , vous définissez et pilotez la stratégie industrielle du site. Vous ête</t>
+          <t>Responsable Supply Chain - Casablanca Achats / Supply Chain - Secteur Agroalimentaire Junior (1 à 3 ans) 1 poste(s) sur Casablanca et région - Maroc Bac +2 Minimum - Ecole de commerce Recherche de nouveauté Respect des règles Besoin d'objectivité Distance émotionnelle Rationalisme Ténacité Besoin d'action Organisation CDI Télétravail : Non Poste avec Management Publiée il y a 20 jours sur ReKrute.com - Postulez avant le 08/09/2026 J'aime Entreprise : Notre société est une entreprise industrielle spécialisée dans la fabrication de biscuits et chocolat. Elle dispose d’un outil de production moderne et en développement constant, conçu pour répondre aux exigences de qualité, de régularité et de performance industrielle. Poste : * Planification et ordonnancement de la production * Gestion des approvisionnements et des stocks * Optimisation des flux logistiques et livraisons clients * Améliora</t>
         </is>
       </c>
     </row>
@@ -11358,15 +11354,19 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur qualité process</t>
+          <t>Responsable Production Senior (H/F) Secteur Aéronautique</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Talents Partners</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr"/>
+          <t>Y STRATEGIE</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="F103" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -11374,12 +11374,12 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Minimum 5 ans</t>
+          <t>Profil senior</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Bouskoura</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -11389,28 +11389,28 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Automobile (caoutchouc)</t>
+          <t>Aéronautique</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>Qualité process</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>Il y a 27 jours</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
       <c r="N103" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma8a7ab40f2b7f3e8b96a4bdf42ad1499f</t>
+          <t>https://ma.linkedin.com/jobs/view/responsable-production-senior-h-f-secteur-a%C3%A9ronautique-at-y-strategie-4436891067</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>Responsable Production Senior (H/F) Casablanca – Bouskoura Notre client est un groupe industriel international de premier plan, spécialisé dans la conception et la fabrication de solutions électroniques et de systèmes d'interconnexion destinés aux secteurs de l'aérospatial, de l'aéronautique, de la défense et des environnements critiques. Dans le cadre du développement de son site de production basé à Casablanca – Bouskoura, il recrute un(e) Responsable Production Senior . Votre mission Rattaché(e) à la Direction Générale , vous définissez et pilotez la stratégie industrielle du site. Vous ête</t>
         </is>
       </c>
     </row>
@@ -11882,19 +11882,15 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Supply Chain Manager</t>
+          <t>Ingénieur Qualité | Tanger (Maroc)</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Hellomaterials</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Relats</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr"/>
       <c r="F111" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -11902,12 +11898,12 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Minimum 4 ans</t>
+          <t>1 à 3 ans minimum</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>Rabat</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
@@ -11917,28 +11913,28 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Matériaux de construction</t>
+          <t>Isolation électrique / Automobile</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>Supply Chain / Qualité</t>
+          <t>Qualité</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>Il y a 1 mois</t>
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/supply-chain-manager-at-hellomaterials-4437123314</t>
+          <t>https://www.optioncarriere.ma/jobad/mae0019487b742a72a1e9a6728319e73c3</t>
         </is>
       </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
-          <t>Poste : Supply Chain &amp; Quality Manager Lieu : Rabat, Agdal (présentiel, 100%) Type de contrat : CDI Salaire net : 8,000 à 15,000 MAD selon profil et expérience Disponibilité : Immédiate POUR POSTULER : Merci de remplir obligatoirement le formulaire suivant : https://forms.gle/QVpjzcH68x1B8NYS6 Toute candidature envoyée uniquement par message LinkedIn ou email ne sera pas traitée. QUI SOMMES-NOUS ? Hellomaterials est une marque internationale spécialisée dans les équipements outdoor premium. Opérant avec une équipe au Maroc. Nous recherchons un(e) Supply Chain &amp; Quality Manager pour piloter l'e</t>
+          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
         </is>
       </c>
     </row>
@@ -11949,15 +11945,19 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Qualité | Tanger (Maroc)</t>
+          <t>Logistique &amp; Supply Chain / Achats - Contrat de Projet | Casablanca (Maroc)</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Relats</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr"/>
+          <t>Manpower Group</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Contrat de projet</t>
+        </is>
+      </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -11965,12 +11965,12 @@
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>1 à 3 ans minimum</t>
+          <t>1 à 3 ans</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>Isolation électrique / Automobile</t>
+          <t>Logistique</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>Qualité</t>
+          <t>Logistique / Achats</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
@@ -11996,7 +11996,7 @@
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mae0019487b742a72a1e9a6728319e73c3</t>
+          <t>https://www.optioncarriere.ma/jobad/ma44800bb0bdfb13c3755b4a5afc1d583d</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Logistique &amp; Supply Chain / Achats - Contrat de Projet | Casablanca (Maroc)</t>
+          <t>Profil Logistique &amp; Supply Chain (Contrat de projet) | Casablanca (Maroc)</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>1 à 3 ans</t>
+          <t>1 à 2 ans</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>Logistique / Achats</t>
+          <t>Logistique / Supply Chain</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
@@ -12063,7 +12063,7 @@
       <c r="M113" s="6" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma44800bb0bdfb13c3755b4a5afc1d583d</t>
+          <t>https://www.optioncarriere.ma/jobad/ma8456e07ad2da184de25cabe4cf9a19c2</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
@@ -12079,19 +12079,11 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Profil Logistique &amp; Supply Chain (Contrat de projet) | Casablanca (Maroc)</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>Manpower Group</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>Contrat de projet</t>
-        </is>
-      </c>
+          <t>Ingénieur Production | Meknès (Maroc)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr"/>
+      <c r="E114" s="11" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -12099,12 +12091,12 @@
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>1 à 2 ans</t>
+          <t>Minimum 2 ans</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Meknes</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -12114,12 +12106,12 @@
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>Logistique</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>Logistique / Supply Chain</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
@@ -12130,7 +12122,7 @@
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma8456e07ad2da184de25cabe4cf9a19c2</t>
+          <t>https://www.optioncarriere.ma/jobad/ma719bbb7ee8694e34f15ecac45b3a77ca</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -12146,10 +12138,14 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Production | Meknès (Maroc)</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr"/>
+          <t>Ingénieur Qualité &amp; Logistique VN (Véhicules Neufs) | Casablanca (Maroc)</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Centrale Automobile Chérifienne (CAC)</t>
+        </is>
+      </c>
       <c r="E115" s="6" t="inlineStr"/>
       <c r="F115" s="14" t="inlineStr">
         <is>
@@ -12158,12 +12154,12 @@
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>Minimum 2 ans</t>
+          <t>2 à 5 ans minimum</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>Meknes</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
@@ -12173,12 +12169,12 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Distribution automobile</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Qualité / Logistique</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -12189,7 +12185,7 @@
       <c r="M115" s="6" t="inlineStr"/>
       <c r="N115" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma719bbb7ee8694e34f15ecac45b3a77ca</t>
+          <t>https://www.optioncarriere.ma/jobad/ma185ae08a3c21be7d0275e68755a62b63</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
@@ -12205,14 +12201,10 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Qualité &amp; Logistique VN (Véhicules Neufs) | Casablanca (Maroc)</t>
-        </is>
-      </c>
-      <c r="D116" s="11" t="inlineStr">
-        <is>
-          <t>Centrale Automobile Chérifienne (CAC)</t>
-        </is>
-      </c>
+          <t>R&amp;D - Manufacturing Engineer</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr"/>
       <c r="E116" s="11" t="inlineStr"/>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -12221,12 +12213,12 @@
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>2 à 5 ans minimum</t>
+          <t>Minimum 2 ans</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -12236,12 +12228,12 @@
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>Distribution automobile</t>
+          <t>Câblage / Assemblage</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>Qualité / Logistique</t>
+          <t>R&amp;D / Manufacturing Engineering</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
@@ -12252,7 +12244,7 @@
       <c r="M116" s="11" t="inlineStr"/>
       <c r="N116" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma185ae08a3c21be7d0275e68755a62b63</t>
+          <t>https://www.optioncarriere.ma/jobad/maac2ff9b46252537caf0b15cbc852ded2</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -12268,7 +12260,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>R&amp;D - Manufacturing Engineer</t>
+          <t>Ingénieur Qualité H/F</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr"/>
@@ -12280,14 +12272,10 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Minimum 2 ans</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>Tanger</t>
-        </is>
-      </c>
+          <t>Minimum 3 ans</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="6" t="inlineStr">
         <is>
           <t>Maroc</t>
@@ -12295,12 +12283,12 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Câblage / Assemblage</t>
+          <t>Aéronautique (composites)</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D / Manufacturing Engineering</t>
+          <t>Qualité</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -12311,7 +12299,7 @@
       <c r="M117" s="6" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/maac2ff9b46252537caf0b15cbc852ded2</t>
+          <t>https://www.optioncarriere.ma/jobad/ma104a2e4a1146bcfdc2c752d13668ba92</t>
         </is>
       </c>
       <c r="O117" s="5" t="inlineStr">
@@ -12327,10 +12315,14 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Qualité H/F</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr"/>
+          <t>Multilingual Supply Chain Engineer | Casablanca (Maroc)</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Capgemini Engineering</t>
+        </is>
+      </c>
       <c r="E118" s="11" t="inlineStr"/>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -12339,10 +12331,14 @@
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>Minimum 3 ans</t>
-        </is>
-      </c>
-      <c r="H118" s="11" t="inlineStr"/>
+          <t>3 à 5 ans</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>Casablanca</t>
+        </is>
+      </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
           <t>Maroc</t>
@@ -12350,12 +12346,12 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>Aéronautique (composites)</t>
+          <t>Services d'ingénierie</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>Qualité</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
@@ -12366,7 +12362,7 @@
       <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma104a2e4a1146bcfdc2c752d13668ba92</t>
+          <t>https://www.optioncarriere.ma/jobad/maaaeb6f7d9a61e4b1fdf0e708acce140d</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -12382,7 +12378,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Multilingual Supply Chain Engineer | Casablanca (Maroc)</t>
+          <t>Multilingual Supply Chain Engineer</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -12390,7 +12386,11 @@
           <t>Capgemini Engineering</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr"/>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="F119" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -12426,10 +12426,14 @@
           <t>Il y a 1 mois</t>
         </is>
       </c>
-      <c r="M119" s="6" t="inlineStr"/>
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="N119" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/maaaeb6f7d9a61e4b1fdf0e708acce140d</t>
+          <t>https://www.optioncarriere.ma/jobad/mabbe19b054c9394a3b677d772a50297d8</t>
         </is>
       </c>
       <c r="O119" s="5" t="inlineStr">
@@ -12445,19 +12449,15 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Multilingual Supply Chain Engineer</t>
+          <t>Ingenieur Logistique</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Capgemini Engineering</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Marocadres</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr"/>
       <c r="F120" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>3 à 5 ans</t>
+          <t>Expérience significative (durée non précisée)</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>Services d'ingénierie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Logistique / Supply Chain</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
@@ -12493,14 +12493,10 @@
           <t>Il y a 1 mois</t>
         </is>
       </c>
-      <c r="M120" s="11" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
+      <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mabbe19b054c9394a3b677d772a50297d8</t>
+          <t>https://www.optioncarriere.ma/jobad/ma7edb35446c48d7d37b0b4f8b9c25a441</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -12516,12 +12512,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Ingenieur Logistique</t>
+          <t>Ingénieur process</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Marocadres</t>
+          <t>Talents Partners</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr"/>
@@ -12532,7 +12528,7 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>Expérience significative (durée non précisée)</t>
+          <t>Minimum 2 ans</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -12547,12 +12543,12 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Automobile (caoutchouc)</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Logistique / Supply Chain</t>
+          <t>Process / Industrialisation</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
@@ -12563,7 +12559,7 @@
       <c r="M121" s="6" t="inlineStr"/>
       <c r="N121" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma7edb35446c48d7d37b0b4f8b9c25a441</t>
+          <t>https://www.optioncarriere.ma/jobad/ma5f90fa62c218dfb14060acb6632bb330</t>
         </is>
       </c>
       <c r="O121" s="5" t="inlineStr">
@@ -12579,12 +12575,12 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur process</t>
+          <t>Ingénieur Process Senior - (DANOMED) | Casablanca (Maroc)</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Talents Partners</t>
+          <t>Danosa Maroc</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr"/>
@@ -12595,12 +12591,12 @@
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>Minimum 2 ans</t>
+          <t>3 à 10 ans</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -12610,7 +12606,7 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>Automobile (caoutchouc)</t>
+          <t>BTP / Chimie</t>
         </is>
       </c>
       <c r="K122" s="11" t="inlineStr">
@@ -12626,7 +12622,7 @@
       <c r="M122" s="11" t="inlineStr"/>
       <c r="N122" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma5f90fa62c218dfb14060acb6632bb330</t>
+          <t>https://www.optioncarriere.ma/jobad/ma8f3b82da366054aa6af4e9b013cbcfed</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -12642,12 +12638,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur Process Senior - (DANOMED) | Casablanca (Maroc)</t>
+          <t>Responsable Production (ovoproduits) | Casablanca (Maroc)</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Danosa Maroc</t>
+          <t>Domino RH</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr"/>
@@ -12658,12 +12654,12 @@
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>3 à 10 ans</t>
+          <t>Expérience impérative en ovoproduits (durée non précisée)</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Nouaceur</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
@@ -12673,12 +12669,12 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>BTP / Chimie</t>
+          <t>Agroalimentaire (ovoproduits)</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>Process / Industrialisation</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
@@ -12689,7 +12685,7 @@
       <c r="M123" s="6" t="inlineStr"/>
       <c r="N123" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma8f3b82da366054aa6af4e9b013cbcfed</t>
+          <t>https://www.optioncarriere.ma/jobad/mae9af357fbf4d5bc3228b5a36e56edee1</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
@@ -12705,12 +12701,12 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Responsable Production (ovoproduits) | Casablanca (Maroc)</t>
+          <t>Responsable Qualité Express | Casablanca (Maroc)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Domino RH</t>
+          <t>Groupe LabelVie (Carrefour Maroc)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr"/>
@@ -12721,12 +12717,12 @@
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>Expérience impérative en ovoproduits (durée non précisée)</t>
+          <t>Au moins 5 ans</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Nouaceur</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -12736,12 +12732,12 @@
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>Agroalimentaire (ovoproduits)</t>
+          <t>Grande distribution</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Qualité</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
@@ -12752,7 +12748,7 @@
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mae9af357fbf4d5bc3228b5a36e56edee1</t>
+          <t>https://www.optioncarriere.ma/jobad/maa205cbfca6244001ddc6c8498d7f0ec2</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -12768,14 +12764,10 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Responsable Qualité Express | Casablanca (Maroc)</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>Groupe LabelVie (Carrefour Maroc)</t>
-        </is>
-      </c>
+          <t>Responsable Supply Chain | Casablanca (Maroc)</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr"/>
       <c r="E125" s="6" t="inlineStr"/>
       <c r="F125" s="14" t="inlineStr">
         <is>
@@ -12784,7 +12776,7 @@
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>Au moins 5 ans</t>
+          <t>Expérience en supply chain industrielle (durée non précisée)</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -12799,12 +12791,12 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Grande distribution</t>
+          <t>Agroalimentaire (biscuiterie / chocolaterie)</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Qualité</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
@@ -12815,7 +12807,7 @@
       <c r="M125" s="6" t="inlineStr"/>
       <c r="N125" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/maa205cbfca6244001ddc6c8498d7f0ec2</t>
+          <t>https://www.optioncarriere.ma/jobad/maa4e9f0265913ca2c8ae1a477de9b4e99</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
@@ -12831,10 +12823,14 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Responsable Supply Chain | Casablanca (Maroc)</t>
-        </is>
-      </c>
-      <c r="D126" s="11" t="inlineStr"/>
+          <t>Senior Supply Chain Engineer | Casablanca (Maroc)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Capgemini Engineering</t>
+        </is>
+      </c>
       <c r="E126" s="11" t="inlineStr"/>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -12843,7 +12839,7 @@
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>Expérience en supply chain industrielle (durée non précisée)</t>
+          <t>3 à 10 ans</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
@@ -12858,7 +12854,7 @@
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>Agroalimentaire (biscuiterie / chocolaterie)</t>
+          <t>Services d'ingénierie</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr">
@@ -12874,7 +12870,7 @@
       <c r="M126" s="11" t="inlineStr"/>
       <c r="N126" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/maa4e9f0265913ca2c8ae1a477de9b4e99</t>
+          <t>https://www.optioncarriere.ma/jobad/mae42dd66a9ddd18a6e45d8434c2101f2b</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -12890,12 +12886,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Senior Supply Chain Engineer | Casablanca (Maroc)</t>
+          <t>Production Manager (H/F) - Tanger</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Capgemini Engineering</t>
+          <t>DEKRA Services</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
@@ -12906,12 +12902,12 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>3 à 10 ans</t>
+          <t>Solide expérience (durée non précisée)</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
@@ -12921,12 +12917,12 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Services d'ingénierie</t>
+          <t>Rubans adhésifs / Automobile</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Direction de production</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
@@ -12937,7 +12933,7 @@
       <c r="M127" s="6" t="inlineStr"/>
       <c r="N127" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mae42dd66a9ddd18a6e45d8434c2101f2b</t>
+          <t>https://www.optioncarriere.ma/jobad/ma9c26ef6e584dea1120ba0491cf7a95fb</t>
         </is>
       </c>
       <c r="O127" s="5" t="inlineStr">
@@ -12953,12 +12949,12 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Production Manager (H/F) - Tanger</t>
+          <t>Plant Manager (H/F) - Salé ou Tanger (Automobile)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>DEKRA Services</t>
+          <t>Michael Page</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr"/>
@@ -12969,7 +12965,7 @@
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>Solide expérience (durée non précisée)</t>
+          <t>Minimum 7 ans</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
@@ -12984,12 +12980,12 @@
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>Rubans adhésifs / Automobile</t>
+          <t>Automobile (systèmes électriques et électroniques)</t>
         </is>
       </c>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>Direction de production</t>
+          <t>Direction de site</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">
@@ -13000,7 +12996,7 @@
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma9c26ef6e584dea1120ba0491cf7a95fb</t>
+          <t>https://www.optioncarriere.ma/jobad/ma9bf7287bac13767e362581c7567d0afa</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -13016,12 +13012,12 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Plant Manager (H/F) - Salé ou Tanger (Automobile)</t>
+          <t>Chef / Responsable Qualité - Meknès</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Michael Page</t>
+          <t>SOMACOS</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr"/>
@@ -13032,12 +13028,12 @@
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>Minimum 7 ans</t>
+          <t>Expérience confirmée en plasturgie (durée non précisée)</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Meknes</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
@@ -13047,12 +13043,12 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Automobile (systèmes électriques et électroniques)</t>
+          <t>Plasturgie</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>Direction de site</t>
+          <t>Qualité</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
@@ -13063,7 +13059,7 @@
       <c r="M129" s="6" t="inlineStr"/>
       <c r="N129" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma9bf7287bac13767e362581c7567d0afa</t>
+          <t>https://www.optioncarriere.ma/jobad/mafeafff839c201687f17007c2ff823044</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
@@ -13079,12 +13075,12 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Chef / Responsable Qualité - Meknès</t>
+          <t>Responsable qualité système (smq)</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>SOMACOS</t>
+          <t>Talents Partners</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr"/>
@@ -13095,12 +13091,12 @@
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>Expérience confirmée en plasturgie (durée non précisée)</t>
+          <t>3 à 5 ans minimum</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Meknes</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -13110,12 +13106,12 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>Plasturgie</t>
+          <t>Automobile (injection plastique)</t>
         </is>
       </c>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>Qualité</t>
+          <t>Qualité système</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
@@ -13126,7 +13122,7 @@
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="12" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/mafeafff839c201687f17007c2ff823044</t>
+          <t>https://www.optioncarriere.ma/jobad/ma9348df82b5400293c1fa7265b0b6b7cd</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -13142,15 +13138,19 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Responsable qualité système (smq)</t>
+          <t>Supply Chain Manager</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Talents Partners</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr"/>
+          <t>Hellomaterials</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="F131" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>3 à 5 ans minimum</t>
+          <t>Minimum 4 ans</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Rabat</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
@@ -13173,28 +13173,28 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Automobile (injection plastique)</t>
+          <t>Matériaux de construction</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>Qualité système</t>
+          <t>Supply Chain / Qualité</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>Il y a 1 mois</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M131" s="6" t="inlineStr"/>
       <c r="N131" s="8" t="inlineStr">
         <is>
-          <t>https://www.optioncarriere.ma/jobad/ma9348df82b5400293c1fa7265b0b6b7cd</t>
+          <t>https://ma.linkedin.com/jobs/view/supply-chain-manager-at-hellomaterials-4437123314</t>
         </is>
       </c>
       <c r="O131" s="5" t="inlineStr">
         <is>
-          <t>Optioncarriere Vérification requise Nos systèmes ont détecté un trafic inhabituel provenant de votre réseau informatique. Cette page vérifie si c'est vraiment vous qui envoyez les requêtes, et non un robot. Adresse IP: 105.190.100.90</t>
+          <t>Poste : Supply Chain &amp; Quality Manager Lieu : Rabat, Agdal (présentiel, 100%) Type de contrat : CDI Salaire net : 8,000 à 15,000 MAD selon profil et expérience Disponibilité : Immédiate POUR POSTULER : Merci de remplir obligatoirement le formulaire suivant : https://forms.gle/QVpjzcH68x1B8NYS6 Toute candidature envoyée uniquement par message LinkedIn ou email ne sera pas traitée. QUI SOMMES-NOUS ? Hellomaterials est une marque internationale spécialisée dans les équipements outdoor premium. Opérant avec une équipe au Maroc. Nous recherchons un(e) Supply Chain &amp; Quality Manager pour piloter l'e</t>
         </is>
       </c>
     </row>
@@ -25762,11 +25762,7 @@
           <t>Senior Business Developer | Casablanca (Morocco)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Rekrute</t>
-        </is>
-      </c>
+      <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="14" t="inlineStr">
         <is>
@@ -25788,7 +25784,11 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Énergie</t>
+        </is>
+      </c>
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
@@ -25814,19 +25814,11 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Ingénieur Commercial H/F</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Clayens NP Morocco</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Commercial /technico commercial</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -25834,12 +25826,12 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Intermédiaire (3 à 5 ans) - Confirmé (5 à 10 ans)</t>
+          <t>1 à 5 ans</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Mohammedia</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -25847,34 +25839,22 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>Plasturgie - Autres Industries</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Commercial / Vente / Export</t>
-        </is>
-      </c>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
+          <t>Hier 16:05</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr"/>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>https://www.rekrute.com/offre-emploi-ingenieur-commercial-hf-recrutement-clayens-np-morocco-mohammedia-184419.html</t>
+          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10424540/commercial-technico-commercial.html</t>
         </is>
       </c>
       <c r="O4" s="10" t="inlineStr">
         <is>
-          <t>CLAYENS NP Morocco recherche un INGÉNIEUR COMMERCIAL H/F à Mohammedia. Vous développerez un portefeuille clients stratégiques, piloterez le cycle de vente complet et assurerez l'interface client. Une expérience industrielle (plasturgie, automobile, aéronautique) et la maîtrise du français/anglais sont requises.</t>
+          <t>commercial /technico commercial Casablanca Publiée le: 3 Aug-16:05 Vue: 60 Annonce N°: 10424540 Dans le cadre du développement de notre activité, nous recherchons des Commerciaux Terrain motivés, dynamiques et orientés résultats pour renforcer notre équipe commerciale. Notre société est spécialisée dans la distribution de produits de sanitaire, plomberie, climatisation, robinetterie industrielle, protection incendie, tubes acier et raccords. Missions principales - Prospecter de nouveaux clients et développer le portefeuille existant. - Assurer la promotion et la vente de nos produits auprès des professionnels. - Identifier les besoins des clients et leur proposer des solutions adaptées. - Négocier les offres commerciales et assurer le suivi des commandes. - Fidéliser les clients en garanti</t>
         </is>
       </c>
     </row>
@@ -25885,17 +25865,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Représentant technico-commercial</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>AIR CI</t>
-        </is>
-      </c>
+          <t>Chargé d'affaires sénior</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -25905,12 +25881,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>1 à 2 ans</t>
+          <t>3 ans minimum</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Agadir</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -25918,30 +25894,22 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Fabrication de machines industrielles</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Ventes et Développement commercial</t>
-        </is>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>Hier 14:59</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/repr%C3%A9sentant-technico-commercial-at-air-ci-4448633197</t>
+          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10427589/chargé-daffaires-sénior.html</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Représentant technico-commercial AIR CI Agadir, Souss-Massa, Maroc il y a 3 heures Postuler Enregistrer - Obtenez des conseils générés par l’IA sur cette offre d‘emploi et d’autres fonctionnalités exclusives. Mon profil convient-il bien pour ce poste ? E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Envoyer un message directement à l’auteur de l’offre d’emploi de AIR CI Mohamed LAARJ Mohamed LAARJ Managing Director | AIR CI | Official Festo Partner in Morocco | Industrial Automation, Pneumatic &amp; Hydraulic Solutions | Comp</t>
+          <t>chargé d'affaires sénior Casablanca Publiée le: 3 Aug-14:59 Vue: 38 Annonce N°: 10427589 Notre structure connaît une forte accélération sur le marché immobilier, et pour accompagner le développement de nos projets, nous recherchons en urgence notre futur(e) Chargé(e) d’Affaires. Vos missions : • Développer et piloter un portefeuille de projets immobiliers. • Structurer les propositions liées aux projets commerciaux et mener les négociations. • Coordonner les échanges avec l'écosystème (Parties concernées, autorités locales, acquéreurs,…etc). Votre profil : • 3 ans d'expérience minimum sur un poste similaire. Domaine : Immobilier Fonction : Négociation/Gestion immobilière Contrat : CDI Entreprise : confidentiel Salaire : A discuter Niveau d'études : Bac plus 5 Ville : Casablanca Annonceur :</t>
         </is>
       </c>
     </row>
@@ -25952,17 +25920,13 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Category Manager / Manager Commercial B2B</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Intelcia Tech</t>
-        </is>
-      </c>
+          <t>Acheteur confirmé</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Temps plein</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -25972,7 +25936,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Cadre</t>
+          <t>3 ans minimum</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -25985,30 +25949,22 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Services et conseil aux entreprises et Commerce de gros</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>Développement commercial et Commerce</t>
-        </is>
-      </c>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>Hier 12:35</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr"/>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/category-manager-manager-commercial-b2b-at-intelcia-tech-4448319065</t>
+          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10427439/acheteur-confirmé.html</t>
         </is>
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>Rejoins Intelcia Tech et transforme l'avenir de l'IT avec nous ! Intelcia Tech est un acteur de référence de l’outsourcing IT et de la transformation digitale. Forts d’une expertise de plus de 20 ans, nous intervenons aujourd’hui dans 5 domaines stratégiques : Infrastructures, Cloud, Solutions Applicatives, Cybersécurité, Data et IA. Avec une équipe dynamique de plus de 800 collaborateurs, nous aidons les entreprises et les institutions publiques à relever leurs défis technologiques grâce à nos centres de services en France, au Maroc, au Cameroun, à Madagascar, au Portugal et en Égypte. Notre mission est de combiner les meilleurs talents avec les dernières technologies de pointe pour proposer des services à forte valeur ajoutée, et qui font la différence. Passionné(e) par la cybersécurité,</t>
+          <t>acheteur confirmé Casablanca Publiée le: 3 Aug-12:35 Vue: 66 Annonce N°: 10427439 L'Acheteur Confirmé la gestion des achats liés aux projets d'éclairage public. Il assure le sourcing, la consultation, la négociation et l'approvisionnement des matériels, équipements et prestations tout en garantissant les meilleures conditions de coût, qualité et délai. • Minimum 3 ans dans les achats techniques. • Une expérience dans les marchés, réseaux électriques BT/HTA ou travaux publics • Connaissance des normes électriques marocaines. • Réseau de fournisseurs dans le domaine de l'éclairage public. • Expérience dans une entreprise de travaux électriques ou d'infrastructures. Domaine : Industrie / Ingénierie / Energie Fonction : Achat Contrat : CDI Entreprise : confidentiel Salaire : A discuter Niveau</t>
         </is>
       </c>
     </row>
@@ -26019,11 +25975,19 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Commercial /technico commercial</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
+          <t>Ingénieur Commercial H/F</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Clayens NP Morocco</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Experimente</t>
@@ -26031,12 +25995,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>1 à 5 ans</t>
+          <t>Intermédiaire (3 à 5 ans) - Confirmé (5 à 10 ans)</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Mohammedia</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -26044,22 +26008,34 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Plasturgie - Autres Industries</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Commercial / Vente / Export</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Hier 16:05</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr"/>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10424540/commercial-technico-commercial.html</t>
+          <t>https://www.rekrute.com/offre-emploi-ingenieur-commercial-hf-recrutement-clayens-np-morocco-mohammedia-184419.html</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>commercial /technico commercial Casablanca Publiée le: 3 Aug-16:05 Vue: 60 Annonce N°: 10424540 Dans le cadre du développement de notre activité, nous recherchons des Commerciaux Terrain motivés, dynamiques et orientés résultats pour renforcer notre équipe commerciale. Notre société est spécialisée dans la distribution de produits de sanitaire, plomberie, climatisation, robinetterie industrielle, protection incendie, tubes acier et raccords. Missions principales - Prospecter de nouveaux clients et développer le portefeuille existant. - Assurer la promotion et la vente de nos produits auprès des professionnels. - Identifier les besoins des clients et leur proposer des solutions adaptées. - Négocier les offres commerciales et assurer le suivi des commandes. - Fidéliser les clients en garanti</t>
+          <t>CLAYENS NP Morocco recherche un INGÉNIEUR COMMERCIAL H/F à Mohammedia. Vous développerez un portefeuille clients stratégiques, piloterez le cycle de vente complet et assurerez l'interface client. Une expérience industrielle (plasturgie, automobile, aéronautique) et la maîtrise du français/anglais sont requises.</t>
         </is>
       </c>
     </row>
@@ -26070,12 +26046,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Account Executive – Senior Manager – Fintech – Morocco, Tunisia, Algeria, Mauritania</t>
+          <t>Représentant technico-commercial</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>AIR CI</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -26090,12 +26066,12 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Cadre</t>
+          <t>1 à 2 ans</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Agadir</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -26105,7 +26081,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Services et conseil en informatique</t>
+          <t>Fabrication de machines industrielles</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
@@ -26121,12 +26097,12 @@
       <c r="M8" s="11" t="inlineStr"/>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/account-executive-%E2%80%93-senior-manager-%E2%80%93-fintech-%E2%80%93-morocco-tunisia-algeria-mauritania-at-visa-4429308340</t>
+          <t>https://ma.linkedin.com/jobs/view/repr%C3%A9sentant-technico-commercial-at-air-ci-4448633197</t>
         </is>
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>About Us Visa is a world leader in payments technology, facilitating transactions between consumers, merchants, financial institutions and government entities across more than 200 countries and territories, dedicated to uplifting everyone, everywhere by being the best way to pay and be paid. At Visa, you'll have the opportunity to create impact at scale — tackling meaningful challenges, growing your skills and seeing your contributions impact lives around the world. Join Visa and do work that matters – to you, to your community, and to the world. Progress starts with you. Job Description The Senior Manager will lead sales and partnership opportunities across fintech and digital banking clients. This role has a broad focus spanning Visa’s three strategic focus areas of Core (Consumer Paymen</t>
+          <t>Représentant technico-commercial AIR CI Agadir, Souss-Massa, Maroc il y a 3 heures Postuler Enregistrer - Obtenez des conseils générés par l’IA sur cette offre d‘emploi et d’autres fonctionnalités exclusives. Mon profil convient-il bien pour ce poste ? E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Envoyer un message directement à l’auteur de l’offre d’emploi de AIR CI Mohamed LAARJ Mohamed LAARJ Managing Director | AIR CI | Official Festo Partner in Morocco | Industrial Automation, Pneumatic &amp; Hydraulic Solutions | Comp</t>
         </is>
       </c>
     </row>
@@ -26137,12 +26113,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Business Development Manager (IQSIGHT) - Morocco</t>
+          <t>Category Manager / Manager Commercial B2B</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Keenfinity Group</t>
+          <t>Intelcia Tech</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -26172,12 +26148,12 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Ingénierie mécanique ou industrielle</t>
+          <t>Services et conseil aux entreprises et Commerce de gros</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Développement commercial</t>
+          <t>Développement commercial et Commerce</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -26188,12 +26164,12 @@
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/business-development-manager-iqsight-morocco-at-keenfinity-group-4448173325</t>
+          <t>https://ma.linkedin.com/jobs/view/category-manager-manager-commercial-b2b-at-intelcia-tech-4448319065</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>Company Description At KEENFINITY, we are a globally leading provider of innovative and professional security and communication solutions. With over 4,000 employees in over 50 countries worldwide, our ambition is clear: we offer more than just technology – we secure, connect, and amplify the moments that matter in life. Next to our passion for technology we’re very passionate about our work environment. Based on values such as trust, appreciation, and accountability we all work together to shape the future – boldly, customer-focused and with a strong team spirit. Job Description We are seeking a highly skilled and detail-oriented Business Development Manager to to join our Video Systems Business and drive business growth across Morocco, Algeria, Tunisia, and Francophone West Africa by iden</t>
+          <t>Rejoins Intelcia Tech et transforme l'avenir de l'IT avec nous ! Intelcia Tech est un acteur de référence de l’outsourcing IT et de la transformation digitale. Forts d’une expertise de plus de 20 ans, nous intervenons aujourd’hui dans 5 domaines stratégiques : Infrastructures, Cloud, Solutions Applicatives, Cybersécurité, Data et IA. Avec une équipe dynamique de plus de 800 collaborateurs, nous aidons les entreprises et les institutions publiques à relever leurs défis technologiques grâce à nos centres de services en France, au Maroc, au Cameroun, à Madagascar, au Portugal et en Égypte. Notre mission est de combiner les meilleurs talents avec les dernières technologies de pointe pour proposer des services à forte valeur ajoutée, et qui font la différence. Passionné(e) par la cybersécurité,</t>
         </is>
       </c>
     </row>
@@ -26204,12 +26180,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Business developer BtoB</t>
+          <t>Account Executive – Senior Manager – Fintech – Morocco, Tunisia, Algeria, Mauritania</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Silkhom | LUNOPA Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -26224,7 +26200,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Confirmé</t>
+          <t>Cadre</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -26239,12 +26215,12 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Fabrication de machines industrielles et Services et conseil en informatique</t>
+          <t>Services et conseil en informatique</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>Technologies de l’information</t>
+          <t>Ventes et Développement commercial</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -26255,12 +26231,12 @@
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/business-developer-btob-at-silkhom-lunopa-group-4432778074</t>
+          <t>https://ma.linkedin.com/jobs/view/account-executive-%E2%80%93-senior-manager-%E2%80%93-fintech-%E2%80%93-morocco-tunisia-algeria-mauritania-at-visa-4429308340</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>Depuis plus de 10 ans, le Groupe Lunopa accompagne les entreprises de toutes tailles (start-up, PME, ETI, grands groupes) dans leurs enjeux de recrutement sur les métiers technologiques, électroniques et industriels. Expert reconnu du conseil en recrutement, LUNOPA Group se positionne comme un acteur de référence dans l'identification, l'évaluation et l'accompagnement des talents en CDI, en freelance ou en prestation externalisée. Nos expertises sont portées par des cabinets spécialisés : - Silkhom – Informatique, Digital, Électronique &amp; Objets Connectés - Silkhom Freelance – Prestations informatiques et électroniques - BlueDocker – Industrie, Logistique &amp; Supply Chain - BluePick – Mise à disposition de freelances industriels Présent à Casablanca et à Lyon, le Groupe Lunopa intervient part</t>
+          <t>About Us Visa is a world leader in payments technology, facilitating transactions between consumers, merchants, financial institutions and government entities across more than 200 countries and territories, dedicated to uplifting everyone, everywhere by being the best way to pay and be paid. At Visa, you'll have the opportunity to create impact at scale — tackling meaningful challenges, growing your skills and seeing your contributions impact lives around the world. Join Visa and do work that matters – to you, to your community, and to the world. Progress starts with you. Job Description The Senior Manager will lead sales and partnership opportunities across fintech and digital banking clients. This role has a broad focus spanning Visa’s three strategic focus areas of Core (Consumer Paymen</t>
         </is>
       </c>
     </row>
@@ -26271,12 +26247,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Acheteur Commodité BIW</t>
+          <t>Business Development Manager (IQSIGHT) - Morocco</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Renault Group</t>
+          <t>Keenfinity Group</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -26291,12 +26267,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Expérience confirmée (durée non précisée)</t>
+          <t>Cadre</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -26306,12 +26282,12 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Fabrication de véhicules automobiles</t>
+          <t>Ingénierie mécanique ou industrielle</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Achats et Chaîne logistique</t>
+          <t>Développement commercial</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -26322,12 +26298,12 @@
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/acheteur-commodit%C3%A9-biw-at-renault-group-4448243670</t>
+          <t>https://ma.linkedin.com/jobs/view/business-development-manager-iqsight-morocco-at-keenfinity-group-4448173325</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>Acheteur Commodité BIW Renault Group Tanger, Tanger-Tétouan-Al Hoceïma, Maroc il y a 4 heures Postuler E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Enregistrer - Au sein de la Direction des Achats du Groupe Renault, vous rejoindrez le service des achats BIW et serez rattaché à son procurement Manager. Une opportunité qui vous permettra d’évoluer dans un environnement internartional, stimulant &amp; challengeant. Le poste est localisé à Tanger. Vous bénéficierez de 2 jours de télétravail Les missions En lien avec des directions telles que l’ingénierie, la logistique ou la qualité, vous vous assurez de la bonne compréhension du besoin d’achat. Dans Le Détail - Vous pilotez l’appel d’offre, participez au choix du fournisseur et vous vo</t>
+          <t>Company Description At KEENFINITY, we are a globally leading provider of innovative and professional security and communication solutions. With over 4,000 employees in over 50 countries worldwide, our ambition is clear: we offer more than just technology – we secure, connect, and amplify the moments that matter in life. Next to our passion for technology we’re very passionate about our work environment. Based on values such as trust, appreciation, and accountability we all work together to shape the future – boldly, customer-focused and with a strong team spirit. Job Description We are seeking a highly skilled and detail-oriented Business Development Manager to to join our Video Systems Business and drive business growth across Morocco, Algeria, Tunisia, and Francophone West Africa by iden</t>
         </is>
       </c>
     </row>
@@ -26338,12 +26314,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Commodity Buyer</t>
+          <t>Business developer BtoB</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Renault Group</t>
+          <t>Silkhom | LUNOPA Group</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -26358,12 +26334,12 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>6 ans minimum</t>
+          <t>Confirmé</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Tanger</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -26373,12 +26349,12 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Fabrication de véhicules automobiles</t>
+          <t>Fabrication de machines industrielles et Services et conseil en informatique</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Achats et Chaîne logistique</t>
+          <t>Technologies de l’information</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -26389,12 +26365,12 @@
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>https://ma.linkedin.com/jobs/view/commodity-buyer-at-renault-group-4447988865</t>
+          <t>https://ma.linkedin.com/jobs/view/business-developer-btob-at-silkhom-lunopa-group-4432778074</t>
         </is>
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>Rattaché(e) au PM Harness, vous serez en charge des achats sur le périmètre Câblage. Vous serez au cœur des relations avec l'Ingénierie, les fournisseurs et les équipes Projet Véhicule dans un esprit de partenariat permettant l’accès à l’innovation, la flexibilité et la performance durable. Vous contribuerez via votre périmètre à la création de valeur pour l'entreprise par la performance QCD de vos pièces. Vos Missions Vous êtes garant de la performance sur le périmètre sous votre responsabilité au sein de la commodité Câblage dans une dynamique d’amélioration continue en respectant les différents jalons du projet Vous êtes en charge des négociations avec les fournisseurs internationaux, en assurant la performance économique, la qualité, les délais de livraison et la conformité RSE. Vous a</t>
+          <t>Depuis plus de 10 ans, le Groupe Lunopa accompagne les entreprises de toutes tailles (start-up, PME, ETI, grands groupes) dans leurs enjeux de recrutement sur les métiers technologiques, électroniques et industriels. Expert reconnu du conseil en recrutement, LUNOPA Group se positionne comme un acteur de référence dans l'identification, l'évaluation et l'accompagnement des talents en CDI, en freelance ou en prestation externalisée. Nos expertises sont portées par des cabinets spécialisés : - Silkhom – Informatique, Digital, Électronique &amp; Objets Connectés - Silkhom Freelance – Prestations informatiques et électroniques - BlueDocker – Industrie, Logistique &amp; Supply Chain - BluePick – Mise à disposition de freelances industriels Présent à Casablanca et à Lyon, le Groupe Lunopa intervient part</t>
         </is>
       </c>
     </row>
@@ -26405,13 +26381,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Chargé d'affaires sénior</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
+          <t>Acheteur Commodité BIW</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Renault Group</t>
+        </is>
+      </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -26421,12 +26401,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>3 ans minimum</t>
+          <t>Expérience confirmée (durée non précisée)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -26434,22 +26414,30 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication de véhicules automobiles</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Achats et Chaîne logistique</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Hier 14:59</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10427589/chargé-daffaires-sénior.html</t>
+          <t>https://ma.linkedin.com/jobs/view/acheteur-commodit%C3%A9-biw-at-renault-group-4448243670</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>chargé d'affaires sénior Casablanca Publiée le: 3 Aug-14:59 Vue: 38 Annonce N°: 10427589 Notre structure connaît une forte accélération sur le marché immobilier, et pour accompagner le développement de nos projets, nous recherchons en urgence notre futur(e) Chargé(e) d’Affaires. Vos missions : • Développer et piloter un portefeuille de projets immobiliers. • Structurer les propositions liées aux projets commerciaux et mener les négociations. • Coordonner les échanges avec l'écosystème (Parties concernées, autorités locales, acquéreurs,…etc). Votre profil : • 3 ans d'expérience minimum sur un poste similaire. Domaine : Immobilier Fonction : Négociation/Gestion immobilière Contrat : CDI Entreprise : confidentiel Salaire : A discuter Niveau d'études : Bac plus 5 Ville : Casablanca Annonceur :</t>
+          <t>Acheteur Commodité BIW Renault Group Tanger, Tanger-Tétouan-Al Hoceïma, Maroc il y a 4 heures Postuler E-mail ou téléphone Mot de passe Afficher S’identifier ou Nouveau sur LinkedIn ? Inscrivez-vous maintenant Enregistrer - Au sein de la Direction des Achats du Groupe Renault, vous rejoindrez le service des achats BIW et serez rattaché à son procurement Manager. Une opportunité qui vous permettra d’évoluer dans un environnement internartional, stimulant &amp; challengeant. Le poste est localisé à Tanger. Vous bénéficierez de 2 jours de télétravail Les missions En lien avec des directions telles que l’ingénierie, la logistique ou la qualité, vous vous assurez de la bonne compréhension du besoin d’achat. Dans Le Détail - Vous pilotez l’appel d’offre, participez au choix du fournisseur et vous vo</t>
         </is>
       </c>
     </row>
@@ -26460,13 +26448,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Acheteur confirmé</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr"/>
+          <t>Commodity Buyer</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Renault Group</t>
+        </is>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Temps plein</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -26476,12 +26468,12 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>3 ans minimum</t>
+          <t>6 ans minimum</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tanger</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -26489,22 +26481,30 @@
           <t>Maroc</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Fabrication de véhicules automobiles</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Achats et Chaîne logistique</t>
+        </is>
+      </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>Hier 12:35</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t>https://www.marocannonces.com/categorie/309/Offres-emploi/annonce/10427439/acheteur-confirmé.html</t>
+          <t>https://ma.linkedin.com/jobs/view/commodity-buyer-at-renault-group-4447988865</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>acheteur confirmé Casablanca Publiée le: 3 Aug-12:35 Vue: 66 Annonce N°: 10427439 L'Acheteur Confirmé la gestion des achats liés aux projets d'éclairage public. Il assure le sourcing, la consultation, la négociation et l'approvisionnement des matériels, équipements et prestations tout en garantissant les meilleures conditions de coût, qualité et délai. • Minimum 3 ans dans les achats techniques. • Une expérience dans les marchés, réseaux électriques BT/HTA ou travaux publics • Connaissance des normes électriques marocaines. • Réseau de fournisseurs dans le domaine de l'éclairage public. • Expérience dans une entreprise de travaux électriques ou d'infrastructures. Domaine : Industrie / Ingénierie / Energie Fonction : Achat Contrat : CDI Entreprise : confidentiel Salaire : A discuter Niveau</t>
+          <t>Rattaché(e) au PM Harness, vous serez en charge des achats sur le périmètre Câblage. Vous serez au cœur des relations avec l'Ingénierie, les fournisseurs et les équipes Projet Véhicule dans un esprit de partenariat permettant l’accès à l’innovation, la flexibilité et la performance durable. Vous contribuerez via votre périmètre à la création de valeur pour l'entreprise par la performance QCD de vos pièces. Vos Missions Vous êtes garant de la performance sur le périmètre sous votre responsabilité au sein de la commodité Câblage dans une dynamique d’amélioration continue en respectant les différents jalons du projet Vous êtes en charge des négociations avec les fournisseurs internationaux, en assurant la performance économique, la qualité, les délais de livraison et la conformité RSE. Vous a</t>
         </is>
       </c>
     </row>
